--- a/Employee_Reports_wi48/Alvin Cataquiz Austria Q0547.xlsx
+++ b/Employee_Reports_wi48/Alvin Cataquiz Austria Q0547.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-405</v>
+        <v>-408</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-333</v>
+        <v>-336</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-129</v>
+        <v>-132</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1533,9 +1533,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>17-Mar-2025</t>
@@ -1547,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-118</v>
+        <v>-121</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1584,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1621,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2044,7 +2056,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2139,7 +2151,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2180,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2197,7 +2209,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2226,7 +2238,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2255,7 +2267,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2284,7 +2296,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2313,7 +2325,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2342,7 +2354,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2371,7 +2383,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2400,7 +2412,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2429,7 +2441,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
